--- a/Production/ReferenceBoard/Reference_Board.xlsx
+++ b/Production/ReferenceBoard/Reference_Board.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kim/Desktop/Lab/Github/PyOpticL_Rubidium_System/Production/ReferenceBoard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF946800-F8D7-B24A-B03E-14DBC86D2968}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BFF94AF-5BFB-E74B-8996-EC0A60A274C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19400" yWindow="740" windowWidth="10000" windowHeight="16680" xr2:uid="{42F6A15E-87CE-9147-9545-45C46C70D310}"/>
   </bookViews>
@@ -49,21 +49,9 @@
     <t>Surface_Adapter_rsp05_lip.step</t>
   </si>
   <si>
-    <t>laser_adaptor.step</t>
-  </si>
-  <si>
     <t>Surface_Adapter_isolator_lip.step</t>
   </si>
   <si>
-    <t>Surface_Adapter_fiberport_lip.step</t>
-  </si>
-  <si>
-    <t>Cube_Mount.step</t>
-  </si>
-  <si>
-    <t>reference_baseboard.step</t>
-  </si>
-  <si>
     <t>M05</t>
   </si>
   <si>
@@ -86,6 +74,18 @@
   </si>
   <si>
     <t>KA05T</t>
+  </si>
+  <si>
+    <t>Cube</t>
+  </si>
+  <si>
+    <t>reference_baseplate.step</t>
+  </si>
+  <si>
+    <t>IPS_adapter.step</t>
+  </si>
+  <si>
+    <t>cube_mount_halfinch.step</t>
   </si>
 </sst>
 </file>
@@ -489,7 +489,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -505,7 +505,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -513,47 +513,47 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B7">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B9">
-        <v>1</v>
+      <c r="B12">
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B13">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="B15">
         <v>7</v>
@@ -561,7 +561,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B16">
         <v>7</v>
@@ -569,7 +569,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B17">
         <v>7</v>
@@ -577,7 +577,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B18">
         <v>7</v>
@@ -585,30 +585,30 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B19">
         <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
-        <v>15</v>
+      <c r="A20" t="s">
+        <v>13</v>
       </c>
       <c r="B20">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A17" r:id="rId1" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=SM05L05" xr:uid="{26D03288-5EB5-E849-A9E7-78F166728512}"/>
-    <hyperlink ref="A18" r:id="rId2" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=SM05FCA2" xr:uid="{7396B97A-1E53-F246-B983-DFB7235DDE2B}"/>
-    <hyperlink ref="A15" r:id="rId3" xr:uid="{1BBCBD75-E5E4-9C42-9870-10D5AFE8751D}"/>
-    <hyperlink ref="A13" r:id="rId4" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=RSP05" xr:uid="{8DD89EFB-A6D7-DC45-81DC-A3DF706D2C18}"/>
-    <hyperlink ref="A14" r:id="rId5" xr:uid="{27DD0994-D2B1-854C-8165-72C16DCFC984}"/>
-    <hyperlink ref="A19" r:id="rId6" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=BB05-E03" xr:uid="{A85C602C-A7C0-4B48-94F9-6B38884C0FD3}"/>
-    <hyperlink ref="A20" r:id="rId7" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=S05TM09" xr:uid="{EF391373-8D5D-B54F-B9A3-5D87DFC3B5D2}"/>
-    <hyperlink ref="A16" r:id="rId8" xr:uid="{2C39C91F-698E-3046-B84D-D54EF6E620B0}"/>
+    <hyperlink ref="A16" r:id="rId1" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=SM05L05" xr:uid="{26D03288-5EB5-E849-A9E7-78F166728512}"/>
+    <hyperlink ref="A17" r:id="rId2" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=SM05FCA2" xr:uid="{7396B97A-1E53-F246-B983-DFB7235DDE2B}"/>
+    <hyperlink ref="A14" r:id="rId3" xr:uid="{1BBCBD75-E5E4-9C42-9870-10D5AFE8751D}"/>
+    <hyperlink ref="A12" r:id="rId4" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=RSP05" xr:uid="{8DD89EFB-A6D7-DC45-81DC-A3DF706D2C18}"/>
+    <hyperlink ref="A13" r:id="rId5" xr:uid="{27DD0994-D2B1-854C-8165-72C16DCFC984}"/>
+    <hyperlink ref="A18" r:id="rId6" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=BB05-E03" xr:uid="{A85C602C-A7C0-4B48-94F9-6B38884C0FD3}"/>
+    <hyperlink ref="A19" r:id="rId7" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=S05TM09" xr:uid="{EF391373-8D5D-B54F-B9A3-5D87DFC3B5D2}"/>
+    <hyperlink ref="A15" r:id="rId8" xr:uid="{2C39C91F-698E-3046-B84D-D54EF6E620B0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
